--- a/files/14-1041-s-corning-st.xlsx
+++ b/files/14-1041-s-corning-st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{326DFAE7-7B9E-4150-8FD8-F09C70669E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DB56160-8691-45E1-93DB-B8042D8833A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6A0F63AB-A391-44B2-B0CA-16F2355589E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{692520FE-9A20-4957-9B7A-6A8E82AE1AC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
     <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Marcus &amp; Millichap, Jul 2026)</t>
   </si>
   <si>
-    <t>NOTE: UNDER CONTRACT per Filip 9/17/26 (confirm which Corning listing). 15 units plus one non-conforming unit per listing | OM: Units 202 and 205 (2 Bd / 2 Ba) are vacant; OM carries them at $2,750 asking rent in current income, which is included in the current GSR of $36,747/mo; Unit count: 15 legal units plus 1 non-conforming single (unit 307, $1,331). Mix rows total 16 rented units; OM $/unit ($313,333) and per-unit expen | OM: Units 202 and 205 (2 Bd / 2 Ba) are vacant; OM carries them at $2,750 asking rent in current income, which is included in the current GSR of $36,747/mo; Unit count: 15 legal units plus 1 non-conforming single (unit 307, $1,331). Mix rows total 16 rented units; OM $/unit ($313,333) and per-unit expen</t>
+    <t>NOTE: UNDER CONTRACT per Filip 9/17/26 (confirm which Corning listing). 15 units plus one non-conforming unit per listing | OM: Units 202 and 205 (2 Bd / 2 Ba) are vacant; OM carries them at $2,750 asking rent in current income, which is included in the current GSR of $36,747/mo; Unit count: 15 legal units plus 1 non-conforming single (unit 307, $1,331). Mix rows total 16 rented units; OM $/unit ($313,333) and per-unit expen</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -697,7 +697,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F880A71-3891-4301-B2A0-6C5DEA708446}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8DCD57-1E64-4142-9463-182E6331C701}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71B4AAD-2F3D-4B37-AE50-4DCC7CF289FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF716EA9-364C-4D1B-B1C8-E4D93F6280F6}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1377,7 +1377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB9783D-FD7D-413B-81B4-312C88D3B3DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504BF3C-0AD8-498C-A066-8E9FD3BD1DF9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2258,7 +2258,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{68DC511A-35B7-41C6-A2D0-3027B20F5753}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{F0112B19-8CE9-4991-90C2-7533475F2C87}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
